--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484200_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484200_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0007</v>
+        <v>4.8567</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5089</v>
+        <v>5.6101</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5083</v>
+        <v>-0.7534</v>
       </c>
       <c r="G2" t="n">
         <v>0.6044</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8697</v>
+        <v>1.7257</v>
       </c>
       <c r="T2" t="n">
-        <v>1.208</v>
+        <v>1.3091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.4167</v>
       </c>
       <c r="V2" t="n">
         <v>0.3778</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.975</v>
+        <v>1.7228</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6853</v>
+        <v>3.2697</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7103</v>
+        <v>-1.5469</v>
       </c>
       <c r="G3" t="n">
         <v>-2.0001</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>2.456</v>
+        <v>1.2038</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5232</v>
+        <v>1.1076</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0672</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>2.7145</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6886</v>
+        <v>1.6267</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8367</v>
+        <v>2.1289</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1481</v>
+        <v>-0.5022</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3209</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6708</v>
+        <v>2.609</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3746</v>
+        <v>1.6668</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2962</v>
+        <v>0.9422</v>
       </c>
       <c r="V4" t="n">
         <v>1.0968</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1547</v>
+        <v>1.5475</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4385</v>
+        <v>2.6408</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2839</v>
+        <v>-1.0932</v>
       </c>
       <c r="G5" t="n">
         <v>2.5923</v>
@@ -844,13 +844,13 @@
         <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2703</v>
+        <v>0.6631</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3193</v>
+        <v>0.5215</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.049</v>
+        <v>0.1416</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7312</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6132</v>
+        <v>-0.3947</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8086</v>
+        <v>-0.1368</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1954</v>
+        <v>-0.258</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9835</v>
+        <v>-1.0447</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.5368</v>
+        <v>-1.2338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5533</v>
+        <v>0.1891</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8847</v>
+        <v>0.4684</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.5736</v>
+        <v>-0.261</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6889</v>
+        <v>0.7294</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0988</v>
+        <v>-1.5131</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9729</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1356</v>
+        <v>-0.5403</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3674</v>
+        <v>1.7719</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6824</v>
+        <v>1.1612</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6849</v>
+        <v>0.6107</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3702</v>
+        <v>-0.7312</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3238</v>
+        <v>1.1638</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9536</v>
+        <v>-1.895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0947</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9457</v>
+        <v>-0.5052</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.149</v>
+        <v>-0.077</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0447</v>
+        <v>-2.9835</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2338</v>
+        <v>-3.5368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1891</v>
+        <v>0.5533</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4684</v>
+        <v>-1.8847</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.261</v>
+        <v>-2.5736</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7294</v>
+        <v>0.6889</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5131</v>
+        <v>-1.0988</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9729</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5403</v>
+        <v>-0.1356</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0719</v>
+        <v>1.3984</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3523</v>
+        <v>0.9858</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7196</v>
+        <v>0.4126</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7312</v>
+        <v>2.3702</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1638</v>
+        <v>3.3238</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.895</v>
+        <v>-0.9536</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5104</v>
+        <v>-1.4831</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0401</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4703</v>
+        <v>-1.4431</v>
       </c>
       <c r="G8" t="n">
         <v>0.1551</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4468</v>
+        <v>-0.4196</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3863</v>
+        <v>-0.3591</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2186</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5643</v>
+        <v>-4.008</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6727</v>
+        <v>-0.4705</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8915</v>
+        <v>-3.5375</v>
       </c>
       <c r="G9" t="n">
         <v>-5.2779</v>
@@ -1156,13 +1156,13 @@
         <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5416</v>
+        <v>1.0979</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8448</v>
+        <v>1.047</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3032</v>
+        <v>0.0508</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6093</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7725</v>
+        <v>-6.0218</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6374</v>
+        <v>-1.1319</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.135</v>
+        <v>-4.8899</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4889</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4556</v>
+        <v>0.2951</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1402</v>
+        <v>0.3653</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3153</v>
+        <v>-0.0702</v>
       </c>
       <c r="V10" t="n">
         <v>-3.6559</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.736100000000001</v>
+        <v>-2.7361</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3649</v>
+        <v>11.365</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.101</v>
+        <v>-14.1012</v>
       </c>
       <c r="G11" t="n">
         <v>-9.764199999999999</v>
@@ -1315,7 +1315,7 @@
         <v>10.3453</v>
       </c>
       <c r="T11" t="n">
-        <v>8.103899999999999</v>
+        <v>8.1038</v>
       </c>
       <c r="U11" t="n">
         <v>2.2415</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.7129</v>
+        <v>5.6852</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5022</v>
+        <v>5.9067</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7893</v>
+        <v>-0.2214</v>
       </c>
       <c r="G12" t="n">
         <v>4.1798</v>
@@ -1390,13 +1390,13 @@
         <v>3.3208</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4113</v>
+        <v>-1.439</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9684</v>
+        <v>-0.5639</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.443</v>
+        <v>-0.8751</v>
       </c>
       <c r="V12" t="n">
         <v>5.4838</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9998</v>
+        <v>4.6688</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7901</v>
+        <v>4.8912</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7903</v>
+        <v>-0.2224</v>
       </c>
       <c r="G13" t="n">
         <v>4.1333</v>
@@ -1468,13 +1468,13 @@
         <v>3.1255</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6024</v>
+        <v>-0.9334</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2943</v>
+        <v>-0.1931</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3081</v>
+        <v>-0.7403</v>
       </c>
       <c r="V13" t="n">
         <v>1.2735</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6625</v>
+        <v>1.8924</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3667</v>
+        <v>3.76</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7042</v>
+        <v>-1.8676</v>
       </c>
       <c r="G14" t="n">
         <v>3.348</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4633</v>
+        <v>-0.3068</v>
       </c>
       <c r="T14" t="n">
-        <v>0.743</v>
+        <v>0.1363</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2797</v>
+        <v>-0.4431</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0188</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>1.261</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2422</v>
+        <v>-0.3825</v>
       </c>
       <c r="G15" t="n">
         <v>2.3922</v>
@@ -1624,13 +1624,13 @@
         <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2217</v>
+        <v>-1.362</v>
       </c>
       <c r="T15" t="n">
         <v>-0.7868000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4349</v>
+        <v>-0.5752</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1052</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4674</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3147</v>
+        <v>-0.8203</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7821</v>
+        <v>1.4317</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6929</v>
@@ -1702,13 +1702,13 @@
         <v>3.3208</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6647</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6219</v>
+        <v>0.1164</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2866</v>
+        <v>-0.6371</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4959</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.353</v>
+        <v>-0.2519</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0609</v>
+        <v>0.162</v>
       </c>
       <c r="F17" t="n">
         <v>-0.414</v>
@@ -1780,10 +1780,10 @@
         <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7451</v>
+        <v>-0.7617</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9731</v>
+        <v>-0.6917</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7182</v>
+        <v>-0.0701</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1959</v>
+        <v>1.3171</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2901</v>
+        <v>3.0842</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-1.7671</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6391</v>
+        <v>1.3928</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9235</v>
+        <v>1.9455</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7156</v>
+        <v>-0.5527</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4431</v>
+        <v>-0.0757</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6334</v>
+        <v>1.1387</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8097</v>
+        <v>-1.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7104</v>
+        <v>-0.9774</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0689</v>
+        <v>-0.4436</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7793</v>
+        <v>-0.5339</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>-1.8828</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1897</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7927999999999999</v>
+        <v>0.872</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3969</v>
+        <v>-1.7727</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3171</v>
+        <v>0.1959</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0842</v>
+        <v>0.2901</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7671</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3928</v>
+        <v>1.6391</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9455</v>
+        <v>0.9235</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>0.7156</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0757</v>
+        <v>-1.4431</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1387</v>
+        <v>-0.6334</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-0.8097</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.7814</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.7581</v>
-      </c>
       <c r="S19" t="n">
-        <v>-1.4054</v>
+        <v>-0.866</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5447</v>
+        <v>-0.0322</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8607</v>
+        <v>-0.8338</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8828</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1805</v>
+        <v>-2.9667</v>
       </c>
       <c r="E20" t="n">
         <v>-1.4908</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6897</v>
+        <v>-1.4759</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7935</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1451</v>
+        <v>-0.9313</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1732</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9719</v>
+        <v>-0.7581</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6568</v>
+        <v>-4.0968</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2546</v>
+        <v>0.2509</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4022</v>
+        <v>-4.3477</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7674</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6475</v>
+        <v>-1.0874</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.4023</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7396</v>
+        <v>-0.6852</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.736300000000001</v>
+        <v>4.758500000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>14.1011</v>
+        <v>14.101</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.3649</v>
+        <v>-9.342599999999999</v>
       </c>
       <c r="G22" t="n">
         <v>9.764099999999999</v>
@@ -2170,13 +2170,13 @@
         <v>19.5342</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.3452</v>
+        <v>-8.322900000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2414</v>
+        <v>-2.2413</v>
       </c>
       <c r="U22" t="n">
-        <v>-8.1038</v>
+        <v>-6.0818</v>
       </c>
       <c r="V22" t="n">
         <v>0.3869000000000002</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484200_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484200_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6267</v>
+        <v>1.5475</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1289</v>
+        <v>2.6408</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5022</v>
+        <v>-1.0932</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3209</v>
+        <v>2.5923</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1302</v>
+        <v>1.2026</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8093</v>
+        <v>1.3897</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1503</v>
+        <v>5.0493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0473</v>
+        <v>2.58</v>
       </c>
       <c r="L4" t="n">
-        <v>3.103</v>
+        <v>2.4694</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4712</v>
+        <v>-2.4571</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1775</v>
+        <v>-1.3773</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2937</v>
+        <v>-1.0797</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>2.609</v>
+        <v>0.6631</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6668</v>
+        <v>0.5215</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9422</v>
+        <v>0.1416</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0968</v>
+        <v>-0.7312</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1219</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5475</v>
+        <v>1.0127</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6408</v>
+        <v>1.5149</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0932</v>
+        <v>-0.5022</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5923</v>
+        <v>-0.9349</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2026</v>
+        <v>-1.7442</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3897</v>
+        <v>0.8093</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0493</v>
+        <v>2.5363</v>
       </c>
       <c r="K5" t="n">
-        <v>2.58</v>
+        <v>-0.5667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4694</v>
+        <v>3.103</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4571</v>
+        <v>-3.4712</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3773</v>
+        <v>-1.1775</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0797</v>
+        <v>-2.2937</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6631</v>
+        <v>2.609</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5215</v>
+        <v>1.6668</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1416</v>
+        <v>0.9422</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7312</v>
+        <v>1.0968</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7312</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3947</v>
+        <v>0.614</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1368</v>
+        <v>0.614</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.258</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0447</v>
+        <v>0.614</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2338</v>
+        <v>0.614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1891</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4684</v>
+        <v>0.614</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.261</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7294</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5131</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9729</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5403</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7719</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1612</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6107</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.895</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.3947</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5052</v>
+        <v>-0.1368</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.077</v>
+        <v>-0.258</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9835</v>
+        <v>-1.0447</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.5368</v>
+        <v>-1.2338</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5533</v>
+        <v>0.1891</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8847</v>
+        <v>0.4684</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5736</v>
+        <v>-0.261</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6889</v>
+        <v>0.7294</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0988</v>
+        <v>-1.5131</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9729</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1356</v>
+        <v>-0.5403</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3984</v>
+        <v>1.7719</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9858</v>
+        <v>1.1612</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4126</v>
+        <v>0.6107</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3702</v>
+        <v>-0.7312</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3238</v>
+        <v>1.1638</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9536</v>
+        <v>-1.895</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4831</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0401</v>
+        <v>-0.5052</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4431</v>
+        <v>-0.077</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1551</v>
+        <v>-2.9835</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1553</v>
+        <v>-3.5368</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0002</v>
+        <v>0.5533</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0205</v>
+        <v>-1.8847</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>-2.5736</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6889</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1346</v>
+        <v>-1.0988</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1348</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>-0.1356</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4196</v>
+        <v>1.3984</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0605</v>
+        <v>0.9858</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3591</v>
+        <v>0.4126</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>2.3702</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-0.9536</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.008</v>
+        <v>-1.4831</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4705</v>
+        <v>-0.0401</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5375</v>
+        <v>-1.4431</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.2779</v>
+        <v>0.1551</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4725</v>
+        <v>0.1553</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8054</v>
+        <v>-0.0002</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1186</v>
+        <v>0.0205</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9555</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.837</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.1593</v>
+        <v>0.1346</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.517</v>
+        <v>0.1348</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.6423</v>
+        <v>-0.0002</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0979</v>
+        <v>-0.4196</v>
       </c>
       <c r="T9" t="n">
-        <v>1.047</v>
+        <v>-0.0605</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0508</v>
+        <v>-0.3591</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1638</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.0218</v>
+        <v>-4.008</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1319</v>
+        <v>-0.4705</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8899</v>
+        <v>-3.5375</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4889</v>
+        <v>-5.2779</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3976</v>
+        <v>-2.4725</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8865</v>
+        <v>-2.8054</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4329</v>
+        <v>-0.1186</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0261</v>
+        <v>-0.9555</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.837</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9219</v>
+        <v>-5.1593</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.517</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2933</v>
+        <v>-3.6423</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2951</v>
+        <v>1.0979</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3653</v>
+        <v>1.047</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0702</v>
+        <v>0.0508</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6559</v>
+        <v>-0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.6559</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7361</v>
+        <v>-6.0218</v>
       </c>
       <c r="E11" t="n">
-        <v>11.365</v>
+        <v>-1.1319</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.1012</v>
+        <v>-4.8899</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.764199999999999</v>
+        <v>-1.4889</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.043500000000001</v>
+        <v>1.3976</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7207</v>
+        <v>-2.8865</v>
       </c>
       <c r="J11" t="n">
-        <v>12.7113</v>
+        <v>1.4329</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2642</v>
+        <v>2.0261</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4473</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-22.4756</v>
+        <v>-2.9219</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.307700000000001</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-14.1679</v>
+        <v>-2.2933</v>
       </c>
       <c r="P11" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-19.5341</v>
-      </c>
       <c r="R11" t="n">
-        <v>16.6042</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>10.3453</v>
+        <v>0.2951</v>
       </c>
       <c r="T11" t="n">
-        <v>8.1038</v>
+        <v>0.3653</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2415</v>
+        <v>-0.0702</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3868999999999989</v>
+        <v>-3.6559</v>
       </c>
       <c r="W11" t="n">
-        <v>10.0841</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.4712</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.6852</v>
+        <v>-2.736099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9067</v>
+        <v>11.365</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2214</v>
+        <v>-14.1012</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1798</v>
+        <v>-9.764199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5927</v>
+        <v>-5.043500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7726</v>
+        <v>-4.7207</v>
       </c>
       <c r="J12" t="n">
-        <v>6.847</v>
+        <v>12.7113</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8148</v>
+        <v>3.2642</v>
       </c>
       <c r="L12" t="n">
-        <v>7.6618</v>
+        <v>9.4473</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6672</v>
+        <v>-22.4756</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7779</v>
+        <v>-8.307700000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8893</v>
+        <v>-14.1679</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5395</v>
+        <v>-2.930099999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8603</v>
+        <v>-19.5341</v>
       </c>
       <c r="R12" t="n">
-        <v>3.3208</v>
+        <v>16.6042</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.439</v>
+        <v>10.3453</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5639</v>
+        <v>8.1038</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8751</v>
+        <v>2.241500000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4838</v>
+        <v>-0.3868999999999989</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4838</v>
+        <v>10.0841</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-10.4712</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6688</v>
+        <v>5.6852</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8912</v>
+        <v>5.9067</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2224</v>
+        <v>-0.2214</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1333</v>
+        <v>4.1798</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9476</v>
+        <v>-1.5927</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1857</v>
+        <v>5.7726</v>
       </c>
       <c r="J13" t="n">
-        <v>6.1866</v>
+        <v>6.847</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8419</v>
+        <v>-0.8148</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3446</v>
+        <v>7.6618</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0532</v>
+        <v>-2.6672</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1057</v>
+        <v>-0.7779</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1589</v>
+        <v>-1.8893</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>-5.8603</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1255</v>
+        <v>3.3208</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9334</v>
+        <v>-1.439</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1931</v>
+        <v>-0.5639</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7403</v>
+        <v>-0.8751</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2735</v>
+        <v>5.4838</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8279</v>
+        <v>5.4838</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8924</v>
+        <v>2.5268</v>
       </c>
       <c r="E14" t="n">
-        <v>3.76</v>
+        <v>2.7493</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8676</v>
+        <v>-0.2224</v>
       </c>
       <c r="G14" t="n">
-        <v>3.348</v>
+        <v>1.9914</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8217</v>
+        <v>0.4127</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5263</v>
+        <v>1.5788</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5073</v>
+        <v>4.0446</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5201</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0128</v>
+        <v>3.7377</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1593</v>
+        <v>-2.0532</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6984</v>
+        <v>0.1057</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>-2.1589</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3068</v>
+        <v>-0.9334</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1363</v>
+        <v>-0.1931</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4431</v>
+        <v>-0.7403</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>1.2735</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0466</v>
+        <v>1.8279</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8784999999999999</v>
+        <v>2.1419</v>
       </c>
       <c r="E15" t="n">
-        <v>1.261</v>
+        <v>2.1419</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3825</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3922</v>
+        <v>2.1419</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4045</v>
+        <v>1.5349</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0122</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3566</v>
+        <v>2.1419</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1543</v>
+        <v>1.5349</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2023</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9643</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2502</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2146</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.362</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5752</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6114000000000001</v>
+        <v>1.8924</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8203</v>
+        <v>3.76</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4317</v>
+        <v>-1.8676</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6929</v>
+        <v>3.348</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3684</v>
+        <v>2.8217</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3245</v>
+        <v>0.5263</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2725</v>
+        <v>3.5073</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1627</v>
+        <v>3.5201</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8902</v>
+        <v>-0.0128</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4204</v>
+        <v>-0.1593</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7944</v>
+        <v>-0.6984</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2148</v>
+        <v>0.5391</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3208</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3208</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.3068</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1164</v>
+        <v>0.1363</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6371</v>
+        <v>-0.4431</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6642</v>
+        <v>3.0466</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2519</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.162</v>
+        <v>1.261</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.414</v>
+        <v>-0.3825</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5484</v>
+        <v>2.3922</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1842</v>
+        <v>3.4045</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3642</v>
+        <v>-1.0122</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0609</v>
+        <v>3.3566</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>3.1543</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>0.2023</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6093</v>
+        <v>-0.9643</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2047</v>
+        <v>0.2502</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4047</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1011</v>
+        <v>-1.362</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1011</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.5752</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7617</v>
+        <v>0.607</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6917</v>
+        <v>0.607</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0701</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3171</v>
+        <v>0.607</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0842</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7671</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3928</v>
+        <v>0.607</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9455</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0757</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1387</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2144</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9774</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4436</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5339</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.0044</v>
       </c>
       <c r="E19" t="n">
-        <v>0.872</v>
+        <v>-1.4273</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7727</v>
+        <v>1.4317</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1959</v>
+        <v>-1.2999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2901</v>
+        <v>-0.3684</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.9315</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6391</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9235</v>
+        <v>-1.1627</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7156</v>
+        <v>0.2833</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4431</v>
+        <v>-0.4204</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6334</v>
+        <v>0.7944</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8097</v>
+        <v>-1.2148</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>3.3208</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>3.3208</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.866</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0322</v>
+        <v>0.1164</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8338</v>
+        <v>-0.6371</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>-1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9667</v>
+        <v>-0.2519</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4908</v>
+        <v>0.162</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4759</v>
+        <v>-0.414</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7935</v>
+        <v>-0.5484</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4026</v>
+        <v>-0.1842</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3908</v>
+        <v>-0.3642</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3409</v>
+        <v>0.0609</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1842</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5251</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4526</v>
+        <v>-0.6093</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5868</v>
+        <v>-0.2047</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1342</v>
+        <v>-0.4047</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9313</v>
+        <v>0.1011</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1732</v>
+        <v>0.1011</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7581</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0968</v>
+        <v>-0.7617</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2509</v>
+        <v>-0.6917</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.3477</v>
+        <v>-0.0701</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7674</v>
+        <v>1.3171</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9566</v>
+        <v>3.0842</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1891</v>
+        <v>-1.7671</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0987</v>
+        <v>1.3928</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3047</v>
+        <v>1.9455</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4035</v>
+        <v>-0.5527</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8662</v>
+        <v>-0.0757</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6518</v>
+        <v>1.1387</v>
       </c>
       <c r="O21" t="n">
         <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0874</v>
+        <v>-0.9774</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4023</v>
+        <v>-0.4436</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6852</v>
+        <v>-0.5339</v>
       </c>
       <c r="V21" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X21" t="n">
         <v>-1.2186</v>
       </c>
-      <c r="W21" t="n">
-        <v>0.5545</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.7731</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,318 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.758500000000002</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="E22" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.7727</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1959</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.09420000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9235</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7156</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.4431</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.6334</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.866</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.8338</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A. MURCIANO PUJADAS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.9667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.4908</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.4759</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.7935</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.4026</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.3908</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.3409</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.5251</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.4526</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.5868</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.9313</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1732</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.7581</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>O. HERAS FLECHA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.0968</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.3477</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.7674</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.9566</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3047</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.4035</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.8662</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.6518</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.2144</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.0874</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4023</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.6852</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484200_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.7584</v>
+      </c>
+      <c r="E25" t="n">
         <v>14.101</v>
       </c>
-      <c r="F22" t="n">
-        <v>-9.342599999999999</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9.764099999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>5.0436</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.7207</v>
-      </c>
-      <c r="J22" t="n">
-        <v>22.4756</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="F25" t="n">
+        <v>-9.342600000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.764100000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.043600000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.720800000000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>22.4755</v>
+      </c>
+      <c r="K25" t="n">
         <v>8.3078</v>
       </c>
-      <c r="L22" t="n">
-        <v>14.1679</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L25" t="n">
+        <v>14.1681</v>
+      </c>
+      <c r="M25" t="n">
         <v>-12.7113</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N25" t="n">
         <v>-3.264</v>
       </c>
-      <c r="O22" t="n">
-        <v>-9.4475</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="O25" t="n">
+        <v>-9.447499999999998</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.929900000000001</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q25" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R25" t="n">
         <v>19.5342</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S25" t="n">
         <v>-8.322900000000001</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>-2.2413</v>
       </c>
-      <c r="U22" t="n">
-        <v>-6.0818</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.3869000000000002</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="U25" t="n">
+        <v>-6.081799999999999</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.3869000000000007</v>
+      </c>
+      <c r="W25" t="n">
         <v>10.4709</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X25" t="n">
         <v>-10.0841</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
